--- a/docs/source/医院内勤规则10.27.xlsx
+++ b/docs/source/医院内勤规则10.27.xlsx
@@ -5,11 +5,11 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\38313\Documents\WPS Cloud Files\.366916517\cachedata\FDA30A63396E4DEDA72C51B5A1B039C3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\张培培\xwechat_files\wxid_w0921z13l6hs22_8d33\msg\file\2026-10\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" tabRatio="938"/>
+    <workbookView windowWidth="22188" windowHeight="11628" tabRatio="938"/>
   </bookViews>
   <sheets>
     <sheet name="账单规则" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="494">
   <si>
     <t>序号</t>
   </si>
@@ -498,9 +498,6 @@
   </si>
   <si>
     <t>敷料包(无纺布)</t>
-  </si>
-  <si>
-    <t>系统价格*0.999</t>
   </si>
   <si>
     <t>附件二：消毒灭菌服务价格表</t>
@@ -3585,7 +3582,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="7543800" cy="5191125"/>
+          <a:ext cx="6789420" cy="5534025"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3632,7 +3629,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="6581775" cy="6924675"/>
+          <a:ext cx="5964555" cy="7381875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3673,8 +3670,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6858000" y="0"/>
-          <a:ext cx="6496050" cy="6838950"/>
+          <a:off x="6172200" y="0"/>
+          <a:ext cx="5878830" cy="7284720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3715,8 +3712,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="7372350"/>
-          <a:ext cx="6467475" cy="4333875"/>
+          <a:off x="617220" y="7863840"/>
+          <a:ext cx="5850255" cy="4619625"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3763,7 +3760,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="6762750" cy="4143375"/>
+          <a:ext cx="6145530" cy="4417695"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3810,7 +3807,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="7543800" cy="4010025"/>
+          <a:ext cx="6789420" cy="4272915"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3857,7 +3854,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="7620000" cy="4762500"/>
+          <a:ext cx="6865620" cy="5071110"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3904,7 +3901,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="6772275" cy="5029200"/>
+          <a:ext cx="6155055" cy="5360670"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3951,7 +3948,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="5629275" cy="6429375"/>
+          <a:ext cx="5080635" cy="6852285"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3998,7 +3995,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="7543800" cy="6610350"/>
+          <a:ext cx="6789420" cy="7044690"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4337,16 +4334,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:J103"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="5" style="25" customWidth="1"/>
     <col min="2" max="2" width="30" style="25" customWidth="1"/>
-    <col min="3" max="6" width="26.8833333333333" style="58" customWidth="1"/>
-    <col min="7" max="8" width="26.8833333333333" style="59" customWidth="1"/>
-    <col min="9" max="10" width="26.8833333333333" style="58" customWidth="1"/>
+    <col min="3" max="6" width="26.8796296296296" style="58" customWidth="1"/>
+    <col min="7" max="8" width="26.8796296296296" style="59" customWidth="1"/>
+    <col min="9" max="10" width="26.8796296296296" style="58" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" spans="1:10">
+    <row r="1" ht="14.4" spans="1:10">
       <c r="A1" s="60" t="s">
         <v>0</v>
       </c>
@@ -4392,7 +4389,7 @@
       </c>
       <c r="J2" s="66"/>
     </row>
-    <row r="3" ht="40.5" spans="1:10">
+    <row r="3" ht="43.2" spans="1:10">
       <c r="A3" s="67">
         <v>1</v>
       </c>
@@ -4524,7 +4521,7 @@
       <c r="I9" s="33"/>
       <c r="J9" s="69"/>
     </row>
-    <row r="10" ht="27" spans="1:10">
+    <row r="10" ht="28.8" spans="1:10">
       <c r="A10" s="67"/>
       <c r="B10" s="36"/>
       <c r="C10" s="4" t="s">
@@ -4542,7 +4539,7 @@
       <c r="I10" s="33"/>
       <c r="J10" s="69"/>
     </row>
-    <row r="11" ht="27" spans="1:10">
+    <row r="11" ht="28.8" spans="1:10">
       <c r="A11" s="67"/>
       <c r="B11" s="36"/>
       <c r="C11" s="4" t="s">
@@ -4560,7 +4557,7 @@
       <c r="I11" s="33"/>
       <c r="J11" s="69"/>
     </row>
-    <row r="12" ht="27" spans="1:10">
+    <row r="12" ht="28.8" spans="1:10">
       <c r="A12" s="67"/>
       <c r="B12" s="36"/>
       <c r="C12" s="4" t="s">
@@ -4614,7 +4611,7 @@
       <c r="I14" s="31"/>
       <c r="J14" s="69"/>
     </row>
-    <row r="15" ht="67.5" spans="1:10">
+    <row r="15" ht="72" spans="1:10">
       <c r="A15" s="67"/>
       <c r="B15" s="36"/>
       <c r="C15" s="4" t="s">
@@ -4634,7 +4631,7 @@
       <c r="I15" s="4"/>
       <c r="J15" s="69"/>
     </row>
-    <row r="16" ht="67.5" spans="1:10">
+    <row r="16" ht="72" spans="1:10">
       <c r="A16" s="67"/>
       <c r="B16" s="36"/>
       <c r="C16" s="4" t="s">
@@ -4654,7 +4651,7 @@
       <c r="I16" s="4"/>
       <c r="J16" s="69"/>
     </row>
-    <row r="17" ht="67.5" spans="1:10">
+    <row r="17" ht="72" spans="1:10">
       <c r="A17" s="67"/>
       <c r="B17" s="36"/>
       <c r="C17" s="4" t="s">
@@ -4674,7 +4671,7 @@
       <c r="I17" s="4"/>
       <c r="J17" s="69"/>
     </row>
-    <row r="18" ht="40.5" spans="1:10">
+    <row r="18" ht="43.2" spans="1:10">
       <c r="A18" s="67"/>
       <c r="B18" s="36"/>
       <c r="C18" s="4" t="s">
@@ -4694,7 +4691,7 @@
       </c>
       <c r="J18" s="69"/>
     </row>
-    <row r="19" ht="40.5" spans="1:10">
+    <row r="19" ht="43.2" spans="1:10">
       <c r="A19" s="67"/>
       <c r="B19" s="36"/>
       <c r="C19" s="4" t="s">
@@ -4712,7 +4709,7 @@
       <c r="I19" s="33"/>
       <c r="J19" s="69"/>
     </row>
-    <row r="20" ht="40.5" spans="1:10">
+    <row r="20" ht="43.2" spans="1:10">
       <c r="A20" s="67"/>
       <c r="B20" s="36"/>
       <c r="C20" s="4" t="s">
@@ -4730,7 +4727,7 @@
       <c r="I20" s="33"/>
       <c r="J20" s="69"/>
     </row>
-    <row r="21" ht="40.5" spans="1:10">
+    <row r="21" ht="43.2" spans="1:10">
       <c r="A21" s="67"/>
       <c r="B21" s="36"/>
       <c r="C21" s="4" t="s">
@@ -4748,7 +4745,7 @@
       <c r="I21" s="33"/>
       <c r="J21" s="69"/>
     </row>
-    <row r="22" ht="40.5" spans="1:10">
+    <row r="22" ht="43.2" spans="1:10">
       <c r="A22" s="67"/>
       <c r="B22" s="36"/>
       <c r="C22" s="4" t="s">
@@ -4766,7 +4763,7 @@
       <c r="I22" s="31"/>
       <c r="J22" s="69"/>
     </row>
-    <row r="23" ht="40.5" spans="1:10">
+    <row r="23" ht="43.2" spans="1:10">
       <c r="A23" s="4">
         <v>2</v>
       </c>
@@ -4972,7 +4969,7 @@
       <c r="I33" s="33"/>
       <c r="J33" s="33"/>
     </row>
-    <row r="34" ht="27" spans="1:10">
+    <row r="34" ht="28.8" spans="1:10">
       <c r="A34" s="4"/>
       <c r="B34" s="33"/>
       <c r="C34" s="4" t="s">
@@ -4990,7 +4987,7 @@
       <c r="I34" s="33"/>
       <c r="J34" s="33"/>
     </row>
-    <row r="35" ht="27" spans="1:10">
+    <row r="35" ht="28.8" spans="1:10">
       <c r="A35" s="4"/>
       <c r="B35" s="33"/>
       <c r="C35" s="4" t="s">
@@ -5008,7 +5005,7 @@
       <c r="I35" s="33"/>
       <c r="J35" s="33"/>
     </row>
-    <row r="36" ht="27" spans="1:10">
+    <row r="36" ht="28.8" spans="1:10">
       <c r="A36" s="4"/>
       <c r="B36" s="33"/>
       <c r="C36" s="4" t="s">
@@ -5062,7 +5059,7 @@
       <c r="I38" s="31"/>
       <c r="J38" s="33"/>
     </row>
-    <row r="39" ht="67.5" spans="1:10">
+    <row r="39" ht="72" spans="1:10">
       <c r="A39" s="4"/>
       <c r="B39" s="33"/>
       <c r="C39" s="4" t="s">
@@ -5082,7 +5079,7 @@
       <c r="I39" s="4"/>
       <c r="J39" s="33"/>
     </row>
-    <row r="40" ht="67.5" spans="1:10">
+    <row r="40" ht="72" spans="1:10">
       <c r="A40" s="4"/>
       <c r="B40" s="33"/>
       <c r="C40" s="4" t="s">
@@ -5102,7 +5099,7 @@
       <c r="I40" s="4"/>
       <c r="J40" s="33"/>
     </row>
-    <row r="41" ht="67.5" spans="1:10">
+    <row r="41" ht="72" spans="1:10">
       <c r="A41" s="4"/>
       <c r="B41" s="33"/>
       <c r="C41" s="4" t="s">
@@ -5122,7 +5119,7 @@
       <c r="I41" s="4"/>
       <c r="J41" s="33"/>
     </row>
-    <row r="42" ht="40.5" spans="1:10">
+    <row r="42" ht="43.2" spans="1:10">
       <c r="A42" s="4"/>
       <c r="B42" s="33"/>
       <c r="C42" s="4" t="s">
@@ -5142,7 +5139,7 @@
       </c>
       <c r="J42" s="33"/>
     </row>
-    <row r="43" ht="40.5" spans="1:10">
+    <row r="43" ht="43.2" spans="1:10">
       <c r="A43" s="4"/>
       <c r="B43" s="33"/>
       <c r="C43" s="4" t="s">
@@ -5160,7 +5157,7 @@
       <c r="I43" s="33"/>
       <c r="J43" s="33"/>
     </row>
-    <row r="44" ht="40.5" spans="1:10">
+    <row r="44" ht="43.2" spans="1:10">
       <c r="A44" s="4"/>
       <c r="B44" s="33"/>
       <c r="C44" s="4" t="s">
@@ -5178,7 +5175,7 @@
       <c r="I44" s="33"/>
       <c r="J44" s="33"/>
     </row>
-    <row r="45" ht="40.5" spans="1:10">
+    <row r="45" ht="43.2" spans="1:10">
       <c r="A45" s="4"/>
       <c r="B45" s="33"/>
       <c r="C45" s="4" t="s">
@@ -5196,7 +5193,7 @@
       <c r="I45" s="33"/>
       <c r="J45" s="33"/>
     </row>
-    <row r="46" ht="40.5" spans="1:10">
+    <row r="46" ht="43.2" spans="1:10">
       <c r="A46" s="4"/>
       <c r="B46" s="31"/>
       <c r="C46" s="4" t="s">
@@ -5214,7 +5211,7 @@
       <c r="I46" s="31"/>
       <c r="J46" s="31"/>
     </row>
-    <row r="47" ht="40.5" spans="1:10">
+    <row r="47" ht="43.2" spans="1:10">
       <c r="A47" s="31">
         <v>3</v>
       </c>
@@ -5572,7 +5569,7 @@
       <c r="I67" s="16"/>
       <c r="J67" s="75"/>
     </row>
-    <row r="68" s="1" customFormat="1" ht="40.5" spans="1:10">
+    <row r="68" s="1" customFormat="1" ht="43.2" spans="1:10">
       <c r="A68" s="2">
         <v>5</v>
       </c>
@@ -5758,7 +5755,7 @@
       <c r="I76" s="85"/>
       <c r="J76" s="14"/>
     </row>
-    <row r="77" customFormat="1" ht="40.5" spans="1:10">
+    <row r="77" customFormat="1" ht="43.2" spans="1:10">
       <c r="A77" s="2"/>
       <c r="B77" s="78"/>
       <c r="C77" s="77" t="s">
@@ -5778,7 +5775,7 @@
       <c r="I77" s="85"/>
       <c r="J77" s="14"/>
     </row>
-    <row r="78" customFormat="1" ht="67.5" spans="1:10">
+    <row r="78" customFormat="1" ht="72" spans="1:10">
       <c r="A78" s="2"/>
       <c r="B78" s="78"/>
       <c r="C78" s="77" t="s">
@@ -5798,7 +5795,7 @@
       <c r="I78" s="85"/>
       <c r="J78" s="14"/>
     </row>
-    <row r="79" customFormat="1" ht="67.5" spans="1:10">
+    <row r="79" customFormat="1" ht="72" spans="1:10">
       <c r="A79" s="2"/>
       <c r="B79" s="78"/>
       <c r="C79" s="77" t="s">
@@ -5818,7 +5815,7 @@
       <c r="I79" s="85"/>
       <c r="J79" s="14"/>
     </row>
-    <row r="80" customFormat="1" ht="67.5" spans="1:10">
+    <row r="80" customFormat="1" ht="72" spans="1:10">
       <c r="A80" s="2"/>
       <c r="B80" s="78"/>
       <c r="C80" s="77" t="s">
@@ -5838,7 +5835,7 @@
       <c r="I80" s="85"/>
       <c r="J80" s="14"/>
     </row>
-    <row r="81" customFormat="1" ht="67.5" spans="1:10">
+    <row r="81" customFormat="1" ht="72" spans="1:10">
       <c r="A81" s="2"/>
       <c r="B81" s="78"/>
       <c r="C81" s="77" t="s">
@@ -5858,7 +5855,7 @@
       <c r="I81" s="85"/>
       <c r="J81" s="14"/>
     </row>
-    <row r="82" customFormat="1" ht="13.5" spans="1:10">
+    <row r="82" customFormat="1" ht="14.4" spans="1:10">
       <c r="A82" s="16">
         <v>6</v>
       </c>
@@ -5878,7 +5875,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="83" customFormat="1" ht="13.5" spans="1:10">
+    <row r="83" customFormat="1" ht="14.4" spans="1:10">
       <c r="A83" s="16">
         <v>7</v>
       </c>
@@ -5898,7 +5895,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="84" customFormat="1" ht="13.5" spans="1:10">
+    <row r="84" customFormat="1" ht="14.4" spans="1:10">
       <c r="A84" s="16">
         <v>8</v>
       </c>
@@ -5918,7 +5915,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="85" customFormat="1" ht="13.5" spans="1:10">
+    <row r="85" customFormat="1" ht="14.4" spans="1:10">
       <c r="A85" s="16">
         <v>9</v>
       </c>
@@ -6085,7 +6082,7 @@
       </c>
       <c r="G93" s="5"/>
       <c r="H93" s="5" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="I93" s="2"/>
       <c r="J93" s="2"/>
@@ -6110,7 +6107,7 @@
       </c>
       <c r="J94" s="2"/>
     </row>
-    <row r="95" customFormat="1" ht="40.5" spans="1:10">
+    <row r="95" customFormat="1" ht="43.2" spans="1:10">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="13" t="s">
@@ -6139,7 +6136,7 @@
       <c r="F96" s="2"/>
       <c r="G96" s="5"/>
       <c r="H96" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I96" s="2"/>
       <c r="J96" s="2"/>
@@ -6267,7 +6264,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="16384" width="9" style="17"/>
   </cols>
@@ -6282,7 +6279,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="16384" width="9" style="17"/>
   </cols>
@@ -6297,7 +6294,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="16384" width="9" style="17"/>
   </cols>
@@ -6313,7 +6310,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -6325,7 +6322,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -6337,14 +6334,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet15"/>
   <dimension ref="A1:J14"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="3" width="39.8916666666667" customWidth="1"/>
+    <col min="2" max="3" width="39.8888888888889" customWidth="1"/>
     <col min="4" max="6" width="8.66666666666667" customWidth="1"/>
-    <col min="7" max="10" width="39.8916666666667" customWidth="1"/>
+    <col min="7" max="10" width="39.8888888888889" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="27" spans="1:10">
+    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:10">
       <c r="A1" s="2">
         <v>5</v>
       </c>
@@ -6370,7 +6367,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" customFormat="1" ht="14.25" spans="1:10">
+    <row r="2" customFormat="1" ht="15.6" spans="1:10">
       <c r="A2" s="2"/>
       <c r="B2" s="8"/>
       <c r="C2" s="9" t="s">
@@ -6390,7 +6387,7 @@
       <c r="I2" s="13"/>
       <c r="J2" s="14"/>
     </row>
-    <row r="3" customFormat="1" ht="14.25" spans="1:10">
+    <row r="3" customFormat="1" ht="15.6" spans="1:10">
       <c r="A3" s="2"/>
       <c r="B3" s="8"/>
       <c r="C3" s="9" t="s">
@@ -6410,7 +6407,7 @@
       <c r="I3" s="13"/>
       <c r="J3" s="14"/>
     </row>
-    <row r="4" customFormat="1" ht="14.25" spans="1:10">
+    <row r="4" customFormat="1" ht="15.6" spans="1:10">
       <c r="A4" s="2"/>
       <c r="B4" s="8"/>
       <c r="C4" s="9" t="s">
@@ -6430,7 +6427,7 @@
       <c r="I4" s="13"/>
       <c r="J4" s="14"/>
     </row>
-    <row r="5" customFormat="1" ht="14.25" spans="1:10">
+    <row r="5" customFormat="1" ht="15.6" spans="1:10">
       <c r="A5" s="2"/>
       <c r="B5" s="8"/>
       <c r="C5" s="9" t="s">
@@ -6450,7 +6447,7 @@
       <c r="I5" s="13"/>
       <c r="J5" s="14"/>
     </row>
-    <row r="6" customFormat="1" ht="14.25" spans="1:10">
+    <row r="6" customFormat="1" ht="15.6" spans="1:10">
       <c r="A6" s="2"/>
       <c r="B6" s="8"/>
       <c r="C6" s="9" t="s">
@@ -6470,7 +6467,7 @@
       <c r="I6" s="13"/>
       <c r="J6" s="14"/>
     </row>
-    <row r="7" customFormat="1" ht="14.25" spans="1:10">
+    <row r="7" customFormat="1" ht="15.6" spans="1:10">
       <c r="A7" s="2"/>
       <c r="B7" s="8"/>
       <c r="C7" s="9" t="s">
@@ -6490,7 +6487,7 @@
       <c r="I7" s="13"/>
       <c r="J7" s="14"/>
     </row>
-    <row r="8" customFormat="1" ht="14.25" spans="1:10">
+    <row r="8" customFormat="1" ht="15.6" spans="1:10">
       <c r="A8" s="2"/>
       <c r="B8" s="8"/>
       <c r="C8" s="9" t="s">
@@ -6510,7 +6507,7 @@
       <c r="I8" s="13"/>
       <c r="J8" s="14"/>
     </row>
-    <row r="9" customFormat="1" ht="14.25" spans="1:10">
+    <row r="9" customFormat="1" ht="15.6" spans="1:10">
       <c r="A9" s="2"/>
       <c r="B9" s="8"/>
       <c r="C9" s="9" t="s">
@@ -6530,7 +6527,7 @@
       <c r="I9" s="13"/>
       <c r="J9" s="14"/>
     </row>
-    <row r="10" customFormat="1" ht="27" spans="1:10">
+    <row r="10" customFormat="1" ht="28.8" spans="1:10">
       <c r="A10" s="2"/>
       <c r="B10" s="8"/>
       <c r="C10" s="4" t="s">
@@ -6550,7 +6547,7 @@
       <c r="I10" s="13"/>
       <c r="J10" s="14"/>
     </row>
-    <row r="11" customFormat="1" ht="40.5" spans="1:10">
+    <row r="11" customFormat="1" ht="43.2" spans="1:10">
       <c r="A11" s="2"/>
       <c r="B11" s="8"/>
       <c r="C11" s="4" t="s">
@@ -6570,7 +6567,7 @@
       <c r="I11" s="13"/>
       <c r="J11" s="14"/>
     </row>
-    <row r="12" customFormat="1" ht="40.5" spans="1:10">
+    <row r="12" customFormat="1" ht="43.2" spans="1:10">
       <c r="A12" s="2"/>
       <c r="B12" s="8"/>
       <c r="C12" s="4" t="s">
@@ -6590,7 +6587,7 @@
       <c r="I12" s="16"/>
       <c r="J12" s="14"/>
     </row>
-    <row r="13" customFormat="1" ht="40.5" spans="1:10">
+    <row r="13" customFormat="1" ht="43.2" spans="1:10">
       <c r="A13" s="2"/>
       <c r="B13" s="8"/>
       <c r="C13" s="4" t="s">
@@ -6610,7 +6607,7 @@
       <c r="I13" s="16"/>
       <c r="J13" s="14"/>
     </row>
-    <row r="14" customFormat="1" ht="40.5" spans="1:10">
+    <row r="14" customFormat="1" ht="43.2" spans="1:10">
       <c r="A14" s="2"/>
       <c r="B14" s="8"/>
       <c r="C14" s="4" t="s">
@@ -6646,18 +6643,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr filterMode="1" codeName="Sheet14"/>
   <dimension ref="A1:F197"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="6.75" style="42" customWidth="1"/>
-    <col min="2" max="2" width="58.3833333333333" style="42" customWidth="1"/>
-    <col min="3" max="4" width="29.6333333333333" style="42" customWidth="1"/>
+    <col min="2" max="2" width="58.3796296296296" style="42" customWidth="1"/>
+    <col min="3" max="4" width="29.6296296296296" style="42" customWidth="1"/>
     <col min="5" max="5" width="18.5" style="42" customWidth="1"/>
     <col min="6" max="16384" width="9" style="41"/>
   </cols>
   <sheetData>
     <row r="1" s="41" customFormat="1" ht="28" customHeight="1" spans="1:6">
       <c r="A1" s="43" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B1" s="43"/>
       <c r="C1" s="43"/>
@@ -6669,19 +6666,19 @@
     </row>
     <row r="2" s="41" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:6">
       <c r="A2" s="44" t="s">
+        <v>101</v>
+      </c>
+      <c r="B2" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="B2" s="44" t="s">
+      <c r="C2" s="44" t="s">
         <v>103</v>
       </c>
-      <c r="C2" s="44" t="s">
+      <c r="D2" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="D2" s="44" t="s">
+      <c r="E2" s="44" t="s">
         <v>105</v>
-      </c>
-      <c r="E2" s="44" t="s">
-        <v>106</v>
       </c>
       <c r="F2" s="45"/>
     </row>
@@ -6693,10 +6690,10 @@
         <v>12</v>
       </c>
       <c r="C3" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="D3" s="44" t="s">
         <v>107</v>
-      </c>
-      <c r="D3" s="44" t="s">
-        <v>108</v>
       </c>
       <c r="E3" s="46">
         <v>8</v>
@@ -6709,10 +6706,10 @@
       </c>
       <c r="B4" s="49"/>
       <c r="C4" s="48" t="s">
+        <v>108</v>
+      </c>
+      <c r="D4" s="44" t="s">
         <v>109</v>
-      </c>
-      <c r="D4" s="44" t="s">
-        <v>110</v>
       </c>
       <c r="E4" s="46">
         <v>12</v>
@@ -6725,10 +6722,10 @@
       </c>
       <c r="B5" s="49"/>
       <c r="C5" s="48" t="s">
+        <v>110</v>
+      </c>
+      <c r="D5" s="44" t="s">
         <v>111</v>
-      </c>
-      <c r="D5" s="44" t="s">
-        <v>112</v>
       </c>
       <c r="E5" s="46">
         <v>31</v>
@@ -6744,7 +6741,7 @@
         <v>47</v>
       </c>
       <c r="D6" s="44" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E6" s="46">
         <v>40</v>
@@ -6757,10 +6754,10 @@
       </c>
       <c r="B7" s="49"/>
       <c r="C7" s="48" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D7" s="44" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E7" s="46">
         <v>40</v>
@@ -6773,7 +6770,7 @@
       </c>
       <c r="B8" s="49"/>
       <c r="C8" s="44" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D8" s="44"/>
       <c r="E8" s="50">
@@ -6787,7 +6784,7 @@
       </c>
       <c r="B9" s="49"/>
       <c r="C9" s="44" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D9" s="44"/>
       <c r="E9" s="46">
@@ -6801,10 +6798,10 @@
       </c>
       <c r="B10" s="49"/>
       <c r="C10" s="48" t="s">
+        <v>116</v>
+      </c>
+      <c r="D10" s="44" t="s">
         <v>117</v>
-      </c>
-      <c r="D10" s="44" t="s">
-        <v>118</v>
       </c>
       <c r="E10" s="46">
         <v>157</v>
@@ -6817,10 +6814,10 @@
       </c>
       <c r="B11" s="49"/>
       <c r="C11" s="44" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D11" s="44" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E11" s="46">
         <v>93</v>
@@ -6833,10 +6830,10 @@
       </c>
       <c r="B12" s="49"/>
       <c r="C12" s="48" t="s">
+        <v>119</v>
+      </c>
+      <c r="D12" s="44" t="s">
         <v>120</v>
-      </c>
-      <c r="D12" s="44" t="s">
-        <v>121</v>
       </c>
       <c r="E12" s="46">
         <v>197</v>
@@ -6849,10 +6846,10 @@
       </c>
       <c r="B13" s="49"/>
       <c r="C13" s="48" t="s">
+        <v>121</v>
+      </c>
+      <c r="D13" s="44" t="s">
         <v>122</v>
-      </c>
-      <c r="D13" s="44" t="s">
-        <v>123</v>
       </c>
       <c r="E13" s="46">
         <v>220</v>
@@ -6865,10 +6862,10 @@
       </c>
       <c r="B14" s="49"/>
       <c r="C14" s="48" t="s">
+        <v>123</v>
+      </c>
+      <c r="D14" s="44" t="s">
         <v>124</v>
-      </c>
-      <c r="D14" s="44" t="s">
-        <v>125</v>
       </c>
       <c r="E14" s="46">
         <v>70</v>
@@ -6881,10 +6878,10 @@
       </c>
       <c r="B15" s="49"/>
       <c r="C15" s="48" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D15" s="44" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E15" s="46">
         <v>25</v>
@@ -6897,7 +6894,7 @@
       </c>
       <c r="B16" s="49"/>
       <c r="C16" s="44" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D16" s="44"/>
       <c r="E16" s="46">
@@ -6911,10 +6908,10 @@
       </c>
       <c r="B17" s="49"/>
       <c r="C17" s="48" t="s">
+        <v>127</v>
+      </c>
+      <c r="D17" s="44" t="s">
         <v>128</v>
-      </c>
-      <c r="D17" s="44" t="s">
-        <v>129</v>
       </c>
       <c r="E17" s="46">
         <v>70</v>
@@ -6927,10 +6924,10 @@
       </c>
       <c r="B18" s="49"/>
       <c r="C18" s="48" t="s">
+        <v>129</v>
+      </c>
+      <c r="D18" s="44" t="s">
         <v>130</v>
-      </c>
-      <c r="D18" s="44" t="s">
-        <v>131</v>
       </c>
       <c r="E18" s="46">
         <v>185</v>
@@ -6943,10 +6940,10 @@
       </c>
       <c r="B19" s="49"/>
       <c r="C19" s="48" t="s">
+        <v>131</v>
+      </c>
+      <c r="D19" s="44" t="s">
         <v>132</v>
-      </c>
-      <c r="D19" s="44" t="s">
-        <v>133</v>
       </c>
       <c r="E19" s="46">
         <v>146</v>
@@ -6959,10 +6956,10 @@
       </c>
       <c r="B20" s="49"/>
       <c r="C20" s="48" t="s">
+        <v>133</v>
+      </c>
+      <c r="D20" s="44" t="s">
         <v>134</v>
-      </c>
-      <c r="D20" s="44" t="s">
-        <v>135</v>
       </c>
       <c r="E20" s="46">
         <v>250</v>
@@ -6975,10 +6972,10 @@
       </c>
       <c r="B21" s="49"/>
       <c r="C21" s="48" t="s">
+        <v>135</v>
+      </c>
+      <c r="D21" s="44" t="s">
         <v>136</v>
-      </c>
-      <c r="D21" s="44" t="s">
-        <v>137</v>
       </c>
       <c r="E21" s="46">
         <v>5</v>
@@ -6991,10 +6988,10 @@
       </c>
       <c r="B22" s="49"/>
       <c r="C22" s="48" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D22" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E22" s="46">
         <v>12</v>
@@ -7007,10 +7004,10 @@
       </c>
       <c r="B23" s="49"/>
       <c r="C23" s="48" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D23" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E23" s="46">
         <v>5</v>
@@ -7023,10 +7020,10 @@
       </c>
       <c r="B24" s="49"/>
       <c r="C24" s="48" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D24" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E24" s="46">
         <v>12</v>
@@ -7039,10 +7036,10 @@
       </c>
       <c r="B25" s="49"/>
       <c r="C25" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="D25" s="44" t="s">
         <v>141</v>
-      </c>
-      <c r="D25" s="44" t="s">
-        <v>142</v>
       </c>
       <c r="E25" s="46">
         <v>25</v>
@@ -7055,10 +7052,10 @@
       </c>
       <c r="B26" s="49"/>
       <c r="C26" s="48" t="s">
+        <v>142</v>
+      </c>
+      <c r="D26" s="44" t="s">
         <v>143</v>
-      </c>
-      <c r="D26" s="44" t="s">
-        <v>144</v>
       </c>
       <c r="E26" s="46">
         <v>10</v>
@@ -7071,10 +7068,10 @@
       </c>
       <c r="B27" s="49"/>
       <c r="C27" s="48" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D27" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E27" s="46">
         <v>5</v>
@@ -7087,10 +7084,10 @@
       </c>
       <c r="B28" s="49"/>
       <c r="C28" s="48" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D28" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E28" s="46">
         <v>8</v>
@@ -7103,7 +7100,7 @@
       </c>
       <c r="B29" s="49"/>
       <c r="C29" s="44" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D29" s="44"/>
       <c r="E29" s="46">
@@ -7117,7 +7114,7 @@
       </c>
       <c r="B30" s="49"/>
       <c r="C30" s="44" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D30" s="44"/>
       <c r="E30" s="46">
@@ -7131,10 +7128,10 @@
       </c>
       <c r="B31" s="49"/>
       <c r="C31" s="48" t="s">
+        <v>135</v>
+      </c>
+      <c r="D31" s="44" t="s">
         <v>136</v>
-      </c>
-      <c r="D31" s="44" t="s">
-        <v>137</v>
       </c>
       <c r="E31" s="46">
         <v>5</v>
@@ -7147,7 +7144,7 @@
       </c>
       <c r="B32" s="49"/>
       <c r="C32" s="44" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D32" s="44"/>
       <c r="E32" s="46">
@@ -7161,10 +7158,10 @@
       </c>
       <c r="B33" s="49"/>
       <c r="C33" s="48" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D33" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E33" s="46">
         <v>5</v>
@@ -7177,7 +7174,7 @@
       </c>
       <c r="B34" s="49"/>
       <c r="C34" s="48" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D34" s="44"/>
       <c r="E34" s="46">
@@ -7191,10 +7188,10 @@
       </c>
       <c r="B35" s="49"/>
       <c r="C35" s="48" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D35" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E35" s="46">
         <v>5</v>
@@ -7207,10 +7204,10 @@
       </c>
       <c r="B36" s="49"/>
       <c r="C36" s="48" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D36" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E36" s="46">
         <v>5</v>
@@ -7223,10 +7220,10 @@
       </c>
       <c r="B37" s="49"/>
       <c r="C37" s="48" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D37" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E37" s="46">
         <v>5</v>
@@ -7239,10 +7236,10 @@
       </c>
       <c r="B38" s="49"/>
       <c r="C38" s="48" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D38" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E38" s="46">
         <v>5</v>
@@ -7255,10 +7252,10 @@
       </c>
       <c r="B39" s="49"/>
       <c r="C39" s="48" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D39" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E39" s="46">
         <v>5</v>
@@ -7271,10 +7268,10 @@
       </c>
       <c r="B40" s="49"/>
       <c r="C40" s="48" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D40" s="44" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E40" s="46">
         <v>12</v>
@@ -7287,10 +7284,10 @@
       </c>
       <c r="B41" s="49"/>
       <c r="C41" s="48" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D41" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E41" s="46">
         <v>5</v>
@@ -7303,10 +7300,10 @@
       </c>
       <c r="B42" s="49"/>
       <c r="C42" s="48" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D42" s="44" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E42" s="46">
         <v>10</v>
@@ -7319,10 +7316,10 @@
       </c>
       <c r="B43" s="49"/>
       <c r="C43" s="48" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D43" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E43" s="46">
         <v>5</v>
@@ -7335,10 +7332,10 @@
       </c>
       <c r="B44" s="49"/>
       <c r="C44" s="48" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D44" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E44" s="46">
         <v>5</v>
@@ -7351,10 +7348,10 @@
       </c>
       <c r="B45" s="49"/>
       <c r="C45" s="48" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D45" s="44" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E45" s="46">
         <v>12</v>
@@ -7367,10 +7364,10 @@
       </c>
       <c r="B46" s="49"/>
       <c r="C46" s="52" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D46" s="52" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E46" s="51">
         <v>25</v>
@@ -7382,10 +7379,10 @@
       </c>
       <c r="B47" s="49"/>
       <c r="C47" s="48" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D47" s="44" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E47" s="46">
         <v>10</v>
@@ -7398,10 +7395,10 @@
       </c>
       <c r="B48" s="49"/>
       <c r="C48" s="48" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D48" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E48" s="46">
         <v>5</v>
@@ -7414,10 +7411,10 @@
       </c>
       <c r="B49" s="49"/>
       <c r="C49" s="48" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D49" s="44" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E49" s="46">
         <v>12</v>
@@ -7430,10 +7427,10 @@
       </c>
       <c r="B50" s="49"/>
       <c r="C50" s="48" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D50" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E50" s="46">
         <v>8</v>
@@ -7446,10 +7443,10 @@
       </c>
       <c r="B51" s="49"/>
       <c r="C51" s="48" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D51" s="44" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E51" s="46">
         <v>12</v>
@@ -7462,10 +7459,10 @@
       </c>
       <c r="B52" s="49"/>
       <c r="C52" s="48" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D52" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E52" s="46">
         <v>5</v>
@@ -7478,10 +7475,10 @@
       </c>
       <c r="B53" s="49"/>
       <c r="C53" s="48" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D53" s="44" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E53" s="46">
         <v>10</v>
@@ -7494,10 +7491,10 @@
       </c>
       <c r="B54" s="49"/>
       <c r="C54" s="52" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D54" s="52" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E54" s="51">
         <v>8</v>
@@ -7509,10 +7506,10 @@
       </c>
       <c r="B55" s="49"/>
       <c r="C55" s="48" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D55" s="44" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E55" s="46">
         <v>12</v>
@@ -7525,10 +7522,10 @@
       </c>
       <c r="B56" s="49"/>
       <c r="C56" s="48" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D56" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E56" s="46">
         <v>5</v>
@@ -7541,10 +7538,10 @@
       </c>
       <c r="B57" s="49"/>
       <c r="C57" s="48" t="s">
+        <v>172</v>
+      </c>
+      <c r="D57" s="44" t="s">
         <v>173</v>
-      </c>
-      <c r="D57" s="44" t="s">
-        <v>174</v>
       </c>
       <c r="E57" s="46">
         <v>10</v>
@@ -7557,10 +7554,10 @@
       </c>
       <c r="B58" s="49"/>
       <c r="C58" s="48" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D58" s="44" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E58" s="46">
         <v>12</v>
@@ -7573,10 +7570,10 @@
       </c>
       <c r="B59" s="49"/>
       <c r="C59" s="48" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D59" s="44" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E59" s="46">
         <v>12</v>
@@ -7589,10 +7586,10 @@
       </c>
       <c r="B60" s="49"/>
       <c r="C60" s="48" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D60" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E60" s="46">
         <v>8</v>
@@ -7605,10 +7602,10 @@
       </c>
       <c r="B61" s="49"/>
       <c r="C61" s="48" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D61" s="44" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E61" s="46">
         <v>10</v>
@@ -7621,10 +7618,10 @@
       </c>
       <c r="B62" s="49"/>
       <c r="C62" s="48" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D62" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E62" s="46">
         <v>5</v>
@@ -7637,10 +7634,10 @@
       </c>
       <c r="B63" s="49"/>
       <c r="C63" s="48" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D63" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E63" s="46">
         <v>8</v>
@@ -7653,10 +7650,10 @@
       </c>
       <c r="B64" s="49"/>
       <c r="C64" s="48" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D64" s="44" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E64" s="46">
         <v>10</v>
@@ -7669,10 +7666,10 @@
       </c>
       <c r="B65" s="49"/>
       <c r="C65" s="48" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D65" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E65" s="46">
         <v>5</v>
@@ -7685,10 +7682,10 @@
       </c>
       <c r="B66" s="49"/>
       <c r="C66" s="48" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D66" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E66" s="46">
         <v>8</v>
@@ -7701,10 +7698,10 @@
       </c>
       <c r="B67" s="49"/>
       <c r="C67" s="48" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D67" s="44" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E67" s="46">
         <v>10</v>
@@ -7717,10 +7714,10 @@
       </c>
       <c r="B68" s="49"/>
       <c r="C68" s="48" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D68" s="44" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E68" s="46">
         <v>10</v>
@@ -7733,10 +7730,10 @@
       </c>
       <c r="B69" s="49"/>
       <c r="C69" s="48" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D69" s="44" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E69" s="46">
         <v>12</v>
@@ -7749,10 +7746,10 @@
       </c>
       <c r="B70" s="49"/>
       <c r="C70" s="48" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D70" s="44" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E70" s="46">
         <v>8</v>
@@ -7765,10 +7762,10 @@
       </c>
       <c r="B71" s="49"/>
       <c r="C71" s="48" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D71" s="44" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E71" s="46">
         <v>8</v>
@@ -7781,10 +7778,10 @@
       </c>
       <c r="B72" s="49"/>
       <c r="C72" s="48" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D72" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E72" s="46">
         <v>5</v>
@@ -7797,10 +7794,10 @@
       </c>
       <c r="B73" s="49"/>
       <c r="C73" s="48" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D73" s="44" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E73" s="46">
         <v>10</v>
@@ -7813,10 +7810,10 @@
       </c>
       <c r="B74" s="49"/>
       <c r="C74" s="48" t="s">
+        <v>188</v>
+      </c>
+      <c r="D74" s="44" t="s">
         <v>189</v>
-      </c>
-      <c r="D74" s="44" t="s">
-        <v>190</v>
       </c>
       <c r="E74" s="46">
         <v>2</v>
@@ -7829,10 +7826,10 @@
       </c>
       <c r="B75" s="49"/>
       <c r="C75" s="48" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D75" s="44" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E75" s="46">
         <v>10</v>
@@ -7845,7 +7842,7 @@
       </c>
       <c r="B76" s="49"/>
       <c r="C76" s="44" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D76" s="44"/>
       <c r="E76" s="46">
@@ -7859,7 +7856,7 @@
       </c>
       <c r="B77" s="49"/>
       <c r="C77" s="44" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D77" s="44"/>
       <c r="E77" s="46">
@@ -7873,7 +7870,7 @@
       </c>
       <c r="B78" s="49"/>
       <c r="C78" s="44" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D78" s="44"/>
       <c r="E78" s="46">
@@ -7887,7 +7884,7 @@
       </c>
       <c r="B79" s="49"/>
       <c r="C79" s="44" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D79" s="44"/>
       <c r="E79" s="46">
@@ -7901,7 +7898,7 @@
       </c>
       <c r="B80" s="49"/>
       <c r="C80" s="44" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D80" s="44"/>
       <c r="E80" s="46">
@@ -7915,7 +7912,7 @@
       </c>
       <c r="B81" s="49"/>
       <c r="C81" s="44" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D81" s="44"/>
       <c r="E81" s="46">
@@ -7929,10 +7926,10 @@
       </c>
       <c r="B82" s="49"/>
       <c r="C82" s="48" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D82" s="44" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E82" s="46">
         <v>160</v>
@@ -7945,7 +7942,7 @@
       </c>
       <c r="B83" s="49"/>
       <c r="C83" s="44" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D83" s="44"/>
       <c r="E83" s="46">
@@ -7959,7 +7956,7 @@
       </c>
       <c r="B84" s="49"/>
       <c r="C84" s="44" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D84" s="44"/>
       <c r="E84" s="46">
@@ -7973,7 +7970,7 @@
       </c>
       <c r="B85" s="49"/>
       <c r="C85" s="44" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D85" s="44"/>
       <c r="E85" s="46">
@@ -7987,10 +7984,10 @@
       </c>
       <c r="B86" s="49"/>
       <c r="C86" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="D86" s="44" t="s">
         <v>202</v>
-      </c>
-      <c r="D86" s="44" t="s">
-        <v>203</v>
       </c>
       <c r="E86" s="46">
         <v>25</v>
@@ -8003,10 +8000,10 @@
       </c>
       <c r="B87" s="49"/>
       <c r="C87" s="48" t="s">
+        <v>203</v>
+      </c>
+      <c r="D87" s="44" t="s">
         <v>204</v>
-      </c>
-      <c r="D87" s="44" t="s">
-        <v>205</v>
       </c>
       <c r="E87" s="46">
         <v>81</v>
@@ -8019,7 +8016,7 @@
       </c>
       <c r="B88" s="49"/>
       <c r="C88" s="44" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D88" s="44"/>
       <c r="E88" s="46">
@@ -8033,10 +8030,10 @@
       </c>
       <c r="B89" s="49"/>
       <c r="C89" s="48" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D89" s="44" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E89" s="46">
         <v>28</v>
@@ -8049,10 +8046,10 @@
       </c>
       <c r="B90" s="49"/>
       <c r="C90" s="48" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D90" s="44" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E90" s="46">
         <v>22</v>
@@ -8065,10 +8062,10 @@
       </c>
       <c r="B91" s="49"/>
       <c r="C91" s="48" t="s">
+        <v>206</v>
+      </c>
+      <c r="D91" s="44" t="s">
         <v>207</v>
-      </c>
-      <c r="D91" s="44" t="s">
-        <v>208</v>
       </c>
       <c r="E91" s="46">
         <v>22</v>
@@ -8081,7 +8078,7 @@
       </c>
       <c r="B92" s="49"/>
       <c r="C92" s="44" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D92" s="44"/>
       <c r="E92" s="46">
@@ -8095,7 +8092,7 @@
       </c>
       <c r="B93" s="49"/>
       <c r="C93" s="44" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D93" s="44"/>
       <c r="E93" s="46">
@@ -8109,7 +8106,7 @@
       </c>
       <c r="B94" s="49"/>
       <c r="C94" s="44" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D94" s="44"/>
       <c r="E94" s="46">
@@ -8123,7 +8120,7 @@
       </c>
       <c r="B95" s="49"/>
       <c r="C95" s="44" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D95" s="44"/>
       <c r="E95" s="46">
@@ -8137,16 +8134,16 @@
       </c>
       <c r="B96" s="49"/>
       <c r="C96" s="53" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D96" s="54" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E96" s="55">
         <v>24</v>
       </c>
       <c r="F96" s="45" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="97" s="41" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:6">
@@ -8155,10 +8152,10 @@
       </c>
       <c r="B97" s="49"/>
       <c r="C97" s="48" t="s">
+        <v>214</v>
+      </c>
+      <c r="D97" s="44" t="s">
         <v>215</v>
-      </c>
-      <c r="D97" s="44" t="s">
-        <v>216</v>
       </c>
       <c r="E97" s="46">
         <v>40</v>
@@ -8171,10 +8168,10 @@
       </c>
       <c r="B98" s="49"/>
       <c r="C98" s="48" t="s">
+        <v>216</v>
+      </c>
+      <c r="D98" s="44" t="s">
         <v>217</v>
-      </c>
-      <c r="D98" s="44" t="s">
-        <v>218</v>
       </c>
       <c r="E98" s="46">
         <v>45</v>
@@ -8187,7 +8184,7 @@
       </c>
       <c r="B99" s="49"/>
       <c r="C99" s="44" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D99" s="44"/>
       <c r="E99" s="46">
@@ -8201,7 +8198,7 @@
       </c>
       <c r="B100" s="49"/>
       <c r="C100" s="44" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D100" s="44"/>
       <c r="E100" s="46">
@@ -8215,10 +8212,10 @@
       </c>
       <c r="B101" s="49"/>
       <c r="C101" s="48" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D101" s="44" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E101" s="46">
         <v>10</v>
@@ -8231,7 +8228,7 @@
       </c>
       <c r="B102" s="49"/>
       <c r="C102" s="44" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D102" s="44"/>
       <c r="E102" s="46">
@@ -8245,10 +8242,10 @@
       </c>
       <c r="B103" s="49"/>
       <c r="C103" s="48" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D103" s="44" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E103" s="46">
         <v>8</v>
@@ -8261,7 +8258,7 @@
       </c>
       <c r="B104" s="49"/>
       <c r="C104" s="44" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D104" s="44"/>
       <c r="E104" s="46">
@@ -8275,10 +8272,10 @@
       </c>
       <c r="B105" s="49"/>
       <c r="C105" s="48" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D105" s="44" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E105" s="46">
         <v>8</v>
@@ -8291,7 +8288,7 @@
       </c>
       <c r="B106" s="49"/>
       <c r="C106" s="44" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D106" s="44"/>
       <c r="E106" s="46">
@@ -8305,7 +8302,7 @@
       </c>
       <c r="B107" s="49"/>
       <c r="C107" s="44" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D107" s="44"/>
       <c r="E107" s="46">
@@ -8319,7 +8316,7 @@
       </c>
       <c r="B108" s="49"/>
       <c r="C108" s="44" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D108" s="44"/>
       <c r="E108" s="46">
@@ -8333,7 +8330,7 @@
       </c>
       <c r="B109" s="49"/>
       <c r="C109" s="44" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D109" s="44"/>
       <c r="E109" s="46">
@@ -8347,7 +8344,7 @@
       </c>
       <c r="B110" s="49"/>
       <c r="C110" s="44" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D110" s="44"/>
       <c r="E110" s="46">
@@ -8361,10 +8358,10 @@
       </c>
       <c r="B111" s="49"/>
       <c r="C111" s="48" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D111" s="44" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E111" s="46">
         <v>24</v>
@@ -8377,10 +8374,10 @@
       </c>
       <c r="B112" s="49"/>
       <c r="C112" s="48" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D112" s="44" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E112" s="46">
         <v>30</v>
@@ -8393,10 +8390,10 @@
       </c>
       <c r="B113" s="49"/>
       <c r="C113" s="48" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D113" s="44" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E113" s="46">
         <v>50</v>
@@ -8409,10 +8406,10 @@
       </c>
       <c r="B114" s="49"/>
       <c r="C114" s="48" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D114" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E114" s="46">
         <v>10</v>
@@ -8425,10 +8422,10 @@
       </c>
       <c r="B115" s="49"/>
       <c r="C115" s="48" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D115" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E115" s="46">
         <v>15</v>
@@ -8441,7 +8438,7 @@
       </c>
       <c r="B116" s="49"/>
       <c r="C116" s="44" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D116" s="44"/>
       <c r="E116" s="46">
@@ -8455,7 +8452,7 @@
       </c>
       <c r="B117" s="49"/>
       <c r="C117" s="44" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D117" s="44"/>
       <c r="E117" s="46">
@@ -8469,10 +8466,10 @@
       </c>
       <c r="B118" s="49"/>
       <c r="C118" s="48" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D118" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E118" s="46">
         <v>15</v>
@@ -8485,10 +8482,10 @@
       </c>
       <c r="B119" s="49"/>
       <c r="C119" s="48" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D119" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E119" s="46">
         <v>15</v>
@@ -8501,7 +8498,7 @@
       </c>
       <c r="B120" s="49"/>
       <c r="C120" s="48" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D120" s="44"/>
       <c r="E120" s="46">
@@ -8515,7 +8512,7 @@
       </c>
       <c r="B121" s="49"/>
       <c r="C121" s="44" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D121" s="44"/>
       <c r="E121" s="46">
@@ -8529,7 +8526,7 @@
       </c>
       <c r="B122" s="49"/>
       <c r="C122" s="44" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D122" s="44"/>
       <c r="E122" s="46">
@@ -8543,7 +8540,7 @@
       </c>
       <c r="B123" s="49"/>
       <c r="C123" s="44" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D123" s="44"/>
       <c r="E123" s="46">
@@ -8557,7 +8554,7 @@
       </c>
       <c r="B124" s="49"/>
       <c r="C124" s="44" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D124" s="44"/>
       <c r="E124" s="46">
@@ -8571,14 +8568,14 @@
       </c>
       <c r="B125" s="49"/>
       <c r="C125" s="54" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D125" s="44"/>
       <c r="E125" s="46">
         <v>5</v>
       </c>
       <c r="F125" s="45" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="126" s="41" customFormat="1" ht="25" hidden="1" customHeight="1" spans="1:6">
@@ -8587,7 +8584,7 @@
       </c>
       <c r="B126" s="49"/>
       <c r="C126" s="44" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D126" s="44"/>
       <c r="E126" s="46">
@@ -8601,7 +8598,7 @@
       </c>
       <c r="B127" s="49"/>
       <c r="C127" s="44" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D127" s="44"/>
       <c r="E127" s="46">
@@ -8615,7 +8612,7 @@
       </c>
       <c r="B128" s="49"/>
       <c r="C128" s="48" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D128" s="44"/>
       <c r="E128" s="46">
@@ -8629,7 +8626,7 @@
       </c>
       <c r="B129" s="49"/>
       <c r="C129" s="48" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D129" s="44"/>
       <c r="E129" s="46">
@@ -8643,7 +8640,7 @@
       </c>
       <c r="B130" s="49"/>
       <c r="C130" s="54" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D130" s="44"/>
       <c r="E130" s="46">
@@ -8657,7 +8654,7 @@
       </c>
       <c r="B131" s="49"/>
       <c r="C131" s="48" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D131" s="44">
         <v>1</v>
@@ -8673,10 +8670,10 @@
       </c>
       <c r="B132" s="49"/>
       <c r="C132" s="48" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D132" s="44" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E132" s="46">
         <v>20</v>
@@ -8689,10 +8686,10 @@
       </c>
       <c r="B133" s="49"/>
       <c r="C133" s="48" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D133" s="44" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E133" s="46">
         <v>50</v>
@@ -8705,10 +8702,10 @@
       </c>
       <c r="B134" s="49"/>
       <c r="C134" s="48" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D134" s="44" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E134" s="46">
         <v>9</v>
@@ -8721,7 +8718,7 @@
       </c>
       <c r="B135" s="49"/>
       <c r="C135" s="44" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D135" s="44"/>
       <c r="E135" s="46">
@@ -8735,7 +8732,7 @@
       </c>
       <c r="B136" s="49"/>
       <c r="C136" s="44" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D136" s="44"/>
       <c r="E136" s="46">
@@ -8749,10 +8746,10 @@
       </c>
       <c r="B137" s="49"/>
       <c r="C137" s="48" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D137" s="44" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E137" s="46">
         <v>140</v>
@@ -8765,10 +8762,10 @@
       </c>
       <c r="B138" s="49"/>
       <c r="C138" s="48" t="s">
+        <v>255</v>
+      </c>
+      <c r="D138" s="44" t="s">
         <v>256</v>
-      </c>
-      <c r="D138" s="44" t="s">
-        <v>257</v>
       </c>
       <c r="E138" s="46">
         <v>140</v>
@@ -8781,7 +8778,7 @@
       </c>
       <c r="B139" s="49"/>
       <c r="C139" s="54" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D139" s="44"/>
       <c r="E139" s="46">
@@ -8795,7 +8792,7 @@
       </c>
       <c r="B140" s="49"/>
       <c r="C140" s="54" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D140" s="44"/>
       <c r="E140" s="46">
@@ -8809,7 +8806,7 @@
       </c>
       <c r="B141" s="49"/>
       <c r="C141" s="44" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D141" s="44"/>
       <c r="E141" s="46">
@@ -8823,7 +8820,7 @@
       </c>
       <c r="B142" s="49"/>
       <c r="C142" s="44" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D142" s="44"/>
       <c r="E142" s="46">
@@ -8837,10 +8834,10 @@
       </c>
       <c r="B143" s="49"/>
       <c r="C143" s="48" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D143" s="44" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E143" s="46">
         <v>12</v>
@@ -8853,7 +8850,7 @@
       </c>
       <c r="B144" s="49"/>
       <c r="C144" s="48" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D144" s="44"/>
       <c r="E144" s="46">
@@ -8867,7 +8864,7 @@
       </c>
       <c r="B145" s="49"/>
       <c r="C145" s="44" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D145" s="44"/>
       <c r="E145" s="46">
@@ -8881,7 +8878,7 @@
       </c>
       <c r="B146" s="49"/>
       <c r="C146" s="44" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D146" s="44"/>
       <c r="E146" s="46">
@@ -8895,7 +8892,7 @@
       </c>
       <c r="B147" s="49"/>
       <c r="C147" s="44" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D147" s="44"/>
       <c r="E147" s="46">
@@ -8909,7 +8906,7 @@
       </c>
       <c r="B148" s="49"/>
       <c r="C148" s="44" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D148" s="44"/>
       <c r="E148" s="46">
@@ -8923,7 +8920,7 @@
       </c>
       <c r="B149" s="49"/>
       <c r="C149" s="44" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D149" s="44"/>
       <c r="E149" s="46">
@@ -8937,7 +8934,7 @@
       </c>
       <c r="B150" s="49"/>
       <c r="C150" s="44" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D150" s="44"/>
       <c r="E150" s="46">
@@ -8951,7 +8948,7 @@
       </c>
       <c r="B151" s="49"/>
       <c r="C151" s="44" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D151" s="44"/>
       <c r="E151" s="46">
@@ -8965,7 +8962,7 @@
       </c>
       <c r="B152" s="49"/>
       <c r="C152" s="44" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D152" s="44"/>
       <c r="E152" s="46">
@@ -8979,7 +8976,7 @@
       </c>
       <c r="B153" s="49"/>
       <c r="C153" s="44" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D153" s="44"/>
       <c r="E153" s="46">
@@ -8993,7 +8990,7 @@
       </c>
       <c r="B154" s="49"/>
       <c r="C154" s="44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D154" s="44"/>
       <c r="E154" s="46">
@@ -9007,7 +9004,7 @@
       </c>
       <c r="B155" s="49"/>
       <c r="C155" s="44" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D155" s="44"/>
       <c r="E155" s="46">
@@ -9021,7 +9018,7 @@
       </c>
       <c r="B156" s="49"/>
       <c r="C156" s="44" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D156" s="44"/>
       <c r="E156" s="46">
@@ -9035,7 +9032,7 @@
       </c>
       <c r="B157" s="49"/>
       <c r="C157" s="44" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D157" s="44"/>
       <c r="E157" s="46">
@@ -9049,10 +9046,10 @@
       </c>
       <c r="B158" s="49"/>
       <c r="C158" s="48" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D158" s="44" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E158" s="46">
         <v>10</v>
@@ -9065,7 +9062,7 @@
       </c>
       <c r="B159" s="49"/>
       <c r="C159" s="44" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D159" s="44"/>
       <c r="E159" s="46">
@@ -9079,7 +9076,7 @@
       </c>
       <c r="B160" s="49"/>
       <c r="C160" s="44" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D160" s="44"/>
       <c r="E160" s="46">
@@ -9093,7 +9090,7 @@
       </c>
       <c r="B161" s="49"/>
       <c r="C161" s="44" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D161" s="44"/>
       <c r="E161" s="46">
@@ -9107,7 +9104,7 @@
       </c>
       <c r="B162" s="49"/>
       <c r="C162" s="44" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D162" s="44"/>
       <c r="E162" s="46">
@@ -9121,7 +9118,7 @@
       </c>
       <c r="B163" s="49"/>
       <c r="C163" s="44" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D163" s="44"/>
       <c r="E163" s="46">
@@ -9135,7 +9132,7 @@
       </c>
       <c r="B164" s="49"/>
       <c r="C164" s="44" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D164" s="44"/>
       <c r="E164" s="46">
@@ -9149,7 +9146,7 @@
       </c>
       <c r="B165" s="49"/>
       <c r="C165" s="44" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D165" s="44"/>
       <c r="E165" s="46">
@@ -9163,7 +9160,7 @@
       </c>
       <c r="B166" s="49"/>
       <c r="C166" s="44" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D166" s="44"/>
       <c r="E166" s="46">
@@ -9177,7 +9174,7 @@
       </c>
       <c r="B167" s="49"/>
       <c r="C167" s="44" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D167" s="44"/>
       <c r="E167" s="46">
@@ -9191,7 +9188,7 @@
       </c>
       <c r="B168" s="49"/>
       <c r="C168" s="44" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D168" s="44"/>
       <c r="E168" s="46">
@@ -9205,7 +9202,7 @@
       </c>
       <c r="B169" s="49"/>
       <c r="C169" s="48" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D169" s="44"/>
       <c r="E169" s="46">
@@ -9219,7 +9216,7 @@
       </c>
       <c r="B170" s="56"/>
       <c r="C170" s="44" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D170" s="44"/>
       <c r="E170" s="46">
@@ -9235,10 +9232,10 @@
         <v>20</v>
       </c>
       <c r="C171" s="48" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D171" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E171" s="46">
         <v>20</v>
@@ -9251,10 +9248,10 @@
       </c>
       <c r="B172" s="46"/>
       <c r="C172" s="48" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D172" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E172" s="46">
         <v>20</v>
@@ -9267,10 +9264,10 @@
       </c>
       <c r="B173" s="46"/>
       <c r="C173" s="48" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D173" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E173" s="46">
         <v>20</v>
@@ -9283,10 +9280,10 @@
       </c>
       <c r="B174" s="46"/>
       <c r="C174" s="48" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D174" s="44" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E174" s="46">
         <v>30</v>
@@ -9299,10 +9296,10 @@
       </c>
       <c r="B175" s="46"/>
       <c r="C175" s="48" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D175" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E175" s="46">
         <v>2</v>
@@ -9315,7 +9312,7 @@
       </c>
       <c r="B176" s="46"/>
       <c r="C176" s="57" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D176" s="52"/>
       <c r="E176" s="51">
@@ -9328,10 +9325,10 @@
       </c>
       <c r="B177" s="46"/>
       <c r="C177" s="52" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D177" s="52" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E177" s="51">
         <v>5</v>
@@ -9343,7 +9340,7 @@
       </c>
       <c r="B178" s="46"/>
       <c r="C178" s="44" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D178" s="44"/>
       <c r="E178" s="46">
@@ -9357,10 +9354,10 @@
       </c>
       <c r="B179" s="46"/>
       <c r="C179" s="44" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D179" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E179" s="46">
         <v>3</v>
@@ -9373,10 +9370,10 @@
       </c>
       <c r="B180" s="46"/>
       <c r="C180" s="48" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D180" s="44" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E180" s="46">
         <v>40</v>
@@ -9389,10 +9386,10 @@
       </c>
       <c r="B181" s="46"/>
       <c r="C181" s="48" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D181" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E181" s="46">
         <v>2</v>
@@ -9405,10 +9402,10 @@
       </c>
       <c r="B182" s="46"/>
       <c r="C182" s="48" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D182" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E182" s="46">
         <v>26</v>
@@ -9421,10 +9418,10 @@
       </c>
       <c r="B183" s="46"/>
       <c r="C183" s="48" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D183" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E183" s="46">
         <v>2</v>
@@ -9437,10 +9434,10 @@
       </c>
       <c r="B184" s="46"/>
       <c r="C184" s="48" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D184" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E184" s="46">
         <v>17</v>
@@ -9453,10 +9450,10 @@
       </c>
       <c r="B185" s="46"/>
       <c r="C185" s="48" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D185" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E185" s="46">
         <v>12</v>
@@ -9469,10 +9466,10 @@
       </c>
       <c r="B186" s="46"/>
       <c r="C186" s="48" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D186" s="44" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E186" s="46">
         <v>30</v>
@@ -9485,10 +9482,10 @@
       </c>
       <c r="B187" s="46"/>
       <c r="C187" s="48" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D187" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E187" s="46">
         <v>17</v>
@@ -9501,10 +9498,10 @@
       </c>
       <c r="B188" s="46"/>
       <c r="C188" s="48" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D188" s="44" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E188" s="46">
         <v>60</v>
@@ -9517,10 +9514,10 @@
       </c>
       <c r="B189" s="46"/>
       <c r="C189" s="48" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D189" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E189" s="46">
         <v>25</v>
@@ -9533,10 +9530,10 @@
       </c>
       <c r="B190" s="46"/>
       <c r="C190" s="48" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D190" s="44" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E190" s="46">
         <v>30</v>
@@ -9549,7 +9546,7 @@
       </c>
       <c r="B191" s="46"/>
       <c r="C191" s="44" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D191" s="44"/>
       <c r="E191" s="46">
@@ -9563,7 +9560,7 @@
       </c>
       <c r="B192" s="46"/>
       <c r="C192" s="44" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D192" s="44"/>
       <c r="E192" s="46">
@@ -9577,7 +9574,7 @@
       </c>
       <c r="B193" s="46"/>
       <c r="C193" s="44" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D193" s="44"/>
       <c r="E193" s="46">
@@ -9591,7 +9588,7 @@
       </c>
       <c r="B194" s="46"/>
       <c r="C194" s="44" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D194" s="44"/>
       <c r="E194" s="46">
@@ -9605,10 +9602,10 @@
       </c>
       <c r="B195" s="46"/>
       <c r="C195" s="48" t="s">
+        <v>311</v>
+      </c>
+      <c r="D195" s="44" t="s">
         <v>312</v>
-      </c>
-      <c r="D195" s="44" t="s">
-        <v>313</v>
       </c>
       <c r="E195" s="46">
         <v>120</v>
@@ -9621,10 +9618,10 @@
       </c>
       <c r="B196" s="46"/>
       <c r="C196" s="48" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D196" s="44" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E196" s="46">
         <v>40</v>
@@ -9637,7 +9634,7 @@
       </c>
       <c r="B197" s="46"/>
       <c r="C197" s="44" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D197" s="44"/>
       <c r="E197" s="46">
@@ -9671,11 +9668,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr filterMode="1" codeName="Sheet8"/>
   <dimension ref="A1:C63"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="11.3833333333333" style="25" customWidth="1"/>
-    <col min="2" max="2" width="49.1333333333333" style="26" customWidth="1"/>
-    <col min="3" max="3" width="49.1333333333333" style="27" customWidth="1"/>
+    <col min="1" max="1" width="11.3796296296296" style="25" customWidth="1"/>
+    <col min="2" max="2" width="49.1296296296296" style="26" customWidth="1"/>
+    <col min="3" max="3" width="49.1296296296296" style="27" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -9686,7 +9683,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="2" hidden="1" spans="1:3">
@@ -9697,14 +9694,14 @@
         <v>72</v>
       </c>
       <c r="C2" s="30" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="3" hidden="1" spans="1:3">
       <c r="A3" s="31"/>
       <c r="B3" s="31"/>
       <c r="C3" s="32" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="4" hidden="1" spans="1:3">
@@ -9715,117 +9712,117 @@
         <v>74</v>
       </c>
       <c r="C4" s="30" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="5" hidden="1" spans="1:3">
       <c r="A5" s="33"/>
       <c r="B5" s="31"/>
       <c r="C5" s="32" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="6" ht="27" hidden="1" spans="1:3">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="6" ht="28.8" hidden="1" spans="1:3">
       <c r="A6" s="29">
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="C6" s="30" t="s">
         <v>320</v>
       </c>
-      <c r="C6" s="30" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="7" ht="27" hidden="1" spans="1:3">
+    </row>
+    <row r="7" ht="43.2" hidden="1" spans="1:3">
       <c r="A7" s="33"/>
       <c r="B7" s="4"/>
       <c r="C7" s="30" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="8" ht="67.5" hidden="1" spans="1:3">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="8" ht="72" hidden="1" spans="1:3">
       <c r="A8" s="33"/>
       <c r="B8" s="4"/>
       <c r="C8" s="30" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9" hidden="1" spans="1:3">
       <c r="A9" s="33"/>
       <c r="B9" s="4"/>
       <c r="C9" s="30" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="10" ht="54" hidden="1" spans="1:3">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="10" ht="72" hidden="1" spans="1:3">
       <c r="A10" s="33"/>
       <c r="B10" s="4"/>
       <c r="C10" s="30" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11" hidden="1" spans="1:3">
       <c r="A11" s="31"/>
       <c r="B11" s="4"/>
       <c r="C11" s="30" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="12" ht="40.5" hidden="1" spans="1:3">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="12" ht="43.2" hidden="1" spans="1:3">
       <c r="A12" s="4">
         <v>4</v>
       </c>
       <c r="B12" s="33" t="s">
+        <v>326</v>
+      </c>
+      <c r="C12" s="30" t="s">
         <v>327</v>
       </c>
-      <c r="C12" s="30" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="13" ht="27" hidden="1" spans="1:3">
+    </row>
+    <row r="13" ht="43.2" hidden="1" spans="1:3">
       <c r="A13" s="4"/>
       <c r="B13" s="33"/>
       <c r="C13" s="30" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="14" ht="67.5" hidden="1" spans="1:3">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="14" ht="72" hidden="1" spans="1:3">
       <c r="A14" s="4"/>
       <c r="B14" s="33"/>
       <c r="C14" s="30" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="15" hidden="1" spans="1:3">
       <c r="A15" s="4"/>
       <c r="B15" s="33"/>
       <c r="C15" s="30" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="16" ht="54" hidden="1" spans="1:3">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="16" ht="72" hidden="1" spans="1:3">
       <c r="A16" s="4"/>
       <c r="B16" s="33"/>
       <c r="C16" s="30" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="17" hidden="1" spans="1:3">
       <c r="A17" s="4"/>
       <c r="B17" s="33"/>
       <c r="C17" s="30" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="18" ht="27" hidden="1" spans="1:3">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="18" ht="28.8" hidden="1" spans="1:3">
       <c r="A18" s="31">
         <v>5</v>
       </c>
       <c r="B18" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>329</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="19" hidden="1" spans="1:3">
@@ -9833,20 +9830,20 @@
         <v>6</v>
       </c>
       <c r="B19" s="29" t="s">
+        <v>330</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>331</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="20" hidden="1" spans="1:3">
       <c r="A20" s="33"/>
       <c r="B20" s="33"/>
       <c r="C20" s="34" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="21" ht="27" hidden="1" spans="1:3">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="21" ht="28.8" hidden="1" spans="1:3">
       <c r="A21" s="33">
         <v>7</v>
       </c>
@@ -9854,14 +9851,14 @@
         <v>86</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="22" hidden="1" spans="1:3">
       <c r="A22" s="31"/>
       <c r="B22" s="31"/>
       <c r="C22" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="23" hidden="1" spans="1:3">
@@ -9869,21 +9866,21 @@
         <v>8</v>
       </c>
       <c r="B23" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="C23" s="4" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="24" ht="40.5" hidden="1" spans="1:3">
+    </row>
+    <row r="24" ht="43.2" hidden="1" spans="1:3">
       <c r="A24" s="31">
         <v>9</v>
       </c>
       <c r="B24" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="C24" s="4" t="s">
         <v>338</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="25" hidden="1" spans="1:3">
@@ -9891,42 +9888,42 @@
         <v>10</v>
       </c>
       <c r="B25" s="35" t="s">
+        <v>339</v>
+      </c>
+      <c r="C25" s="28" t="s">
         <v>340</v>
-      </c>
-      <c r="C25" s="28" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="26" hidden="1" spans="1:3">
       <c r="A26" s="36"/>
       <c r="B26" s="37"/>
       <c r="C26" s="34" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="27" ht="81" hidden="1" spans="1:3">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="27" ht="86.4" hidden="1" spans="1:3">
       <c r="A27" s="33">
         <v>11</v>
       </c>
       <c r="B27" s="29" t="s">
+        <v>342</v>
+      </c>
+      <c r="C27" s="4" t="s">
         <v>343</v>
       </c>
-      <c r="C27" s="4" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="28" ht="40.5" hidden="1" spans="1:3">
+    </row>
+    <row r="28" ht="43.2" hidden="1" spans="1:3">
       <c r="A28" s="33"/>
       <c r="B28" s="33"/>
       <c r="C28" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="29" hidden="1" spans="1:3">
       <c r="A29" s="31"/>
       <c r="B29" s="31"/>
       <c r="C29" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -9934,38 +9931,38 @@
         <v>12</v>
       </c>
       <c r="B30" s="38" t="s">
+        <v>346</v>
+      </c>
+      <c r="C30" s="4" t="s">
         <v>347</v>
       </c>
-      <c r="C30" s="4" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="31" ht="40.5" spans="1:3">
+    </row>
+    <row r="31" ht="43.2" spans="1:3">
       <c r="A31" s="33"/>
       <c r="B31" s="36"/>
       <c r="C31" s="4" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="32" ht="121.5" spans="1:3">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="32" ht="144" spans="1:3">
       <c r="A32" s="33"/>
       <c r="B32" s="36"/>
       <c r="C32" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="33"/>
       <c r="B33" s="36"/>
       <c r="C33" s="34" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="33"/>
       <c r="B34" s="36"/>
       <c r="C34" s="34" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="35" hidden="1" spans="1:3">
@@ -9973,24 +9970,24 @@
         <v>13</v>
       </c>
       <c r="B35" s="29" t="s">
+        <v>352</v>
+      </c>
+      <c r="C35" s="4" t="s">
         <v>353</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="36" hidden="1" spans="1:3">
       <c r="A36" s="4"/>
       <c r="B36" s="33"/>
       <c r="C36" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="37" hidden="1" spans="1:3">
       <c r="A37" s="4"/>
       <c r="B37" s="31"/>
       <c r="C37" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="38" hidden="1" spans="1:3">
@@ -9998,42 +9995,42 @@
         <v>14</v>
       </c>
       <c r="B38" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="C38" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="C38" s="4" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="39" ht="121.5" hidden="1" spans="1:3">
+    </row>
+    <row r="39" ht="144" hidden="1" spans="1:3">
       <c r="A39" s="4">
         <v>15</v>
       </c>
       <c r="B39" s="29" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="40" ht="40.5" hidden="1" spans="1:3">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="40" ht="43.2" hidden="1" spans="1:3">
       <c r="A40" s="4"/>
       <c r="B40" s="33"/>
       <c r="C40" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="41" hidden="1" spans="1:3">
       <c r="A41" s="4"/>
       <c r="B41" s="33"/>
       <c r="C41" s="34" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="42" hidden="1" spans="1:3">
       <c r="A42" s="4"/>
       <c r="B42" s="33"/>
       <c r="C42" s="34" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="43" hidden="1" spans="1:3">
@@ -10041,28 +10038,28 @@
         <v>16</v>
       </c>
       <c r="B43" s="29" t="s">
+        <v>358</v>
+      </c>
+      <c r="C43" s="4" t="s">
         <v>359</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="44" hidden="1" spans="1:3">
       <c r="A44" s="31"/>
       <c r="B44" s="31"/>
       <c r="C44" s="4" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="45" ht="40.5" hidden="1" spans="1:3">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="45" ht="43.2" hidden="1" spans="1:3">
       <c r="A45" s="31">
         <v>17</v>
       </c>
       <c r="B45" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="C45" s="39" t="s">
         <v>362</v>
-      </c>
-      <c r="C45" s="39" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="46" hidden="1" spans="1:3">
@@ -10070,17 +10067,17 @@
         <v>18</v>
       </c>
       <c r="B46" s="29" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="47" ht="27" hidden="1" spans="1:3">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="47" ht="28.8" hidden="1" spans="1:3">
       <c r="A47" s="31"/>
       <c r="B47" s="31"/>
       <c r="C47" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="48" hidden="1" spans="1:3">
@@ -10088,24 +10085,24 @@
         <v>19</v>
       </c>
       <c r="B48" s="33" t="s">
+        <v>365</v>
+      </c>
+      <c r="C48" s="4" t="s">
         <v>366</v>
       </c>
-      <c r="C48" s="4" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="49" ht="27" hidden="1" spans="1:3">
+    </row>
+    <row r="49" ht="28.8" hidden="1" spans="1:3">
       <c r="A49" s="33"/>
       <c r="B49" s="33"/>
       <c r="C49" s="4" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="50" ht="40.5" hidden="1" spans="1:3">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="50" ht="43.2" hidden="1" spans="1:3">
       <c r="A50" s="31"/>
       <c r="B50" s="31"/>
       <c r="C50" s="4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -10113,17 +10110,17 @@
         <v>20</v>
       </c>
       <c r="B51" s="29" t="s">
+        <v>369</v>
+      </c>
+      <c r="C51" s="39" t="s">
         <v>370</v>
-      </c>
-      <c r="C51" s="39" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="31"/>
       <c r="B52" s="31"/>
       <c r="C52" s="34" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="53" hidden="1" spans="1:3">
@@ -10131,17 +10128,17 @@
         <v>21</v>
       </c>
       <c r="B53" s="29" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C53" s="39" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="54" hidden="1" spans="1:3">
       <c r="A54" s="31"/>
       <c r="B54" s="31"/>
       <c r="C54" s="34" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="55" hidden="1" spans="1:3">
@@ -10149,10 +10146,10 @@
         <v>22</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C55" s="39" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="56" hidden="1" spans="1:3">
@@ -10160,10 +10157,10 @@
         <v>23</v>
       </c>
       <c r="B56" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="C56" s="4" t="s">
         <v>375</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="57" hidden="1" spans="1:3">
@@ -10171,39 +10168,39 @@
         <v>24</v>
       </c>
       <c r="B57" s="29" t="s">
+        <v>376</v>
+      </c>
+      <c r="C57" s="4" t="s">
         <v>377</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="58" hidden="1" spans="1:3">
       <c r="A58" s="31"/>
       <c r="B58" s="31"/>
       <c r="C58" s="34" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="59" ht="27" hidden="1" spans="1:3">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="59" ht="28.8" hidden="1" spans="1:3">
       <c r="A59" s="31">
         <v>25</v>
       </c>
       <c r="B59" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="C59" s="4" t="s">
         <v>379</v>
       </c>
-      <c r="C59" s="4" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="60" ht="27" hidden="1" spans="1:3">
+    </row>
+    <row r="60" ht="28.8" hidden="1" spans="1:3">
       <c r="A60" s="31">
         <v>26</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="61" hidden="1" spans="1:3">
@@ -10211,10 +10208,10 @@
         <v>27</v>
       </c>
       <c r="B61" s="40" t="s">
+        <v>381</v>
+      </c>
+      <c r="C61" s="40" t="s">
         <v>382</v>
-      </c>
-      <c r="C61" s="40" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="62" hidden="1" spans="1:3">
@@ -10222,10 +10219,10 @@
         <v>28</v>
       </c>
       <c r="B62" s="40" t="s">
+        <v>383</v>
+      </c>
+      <c r="C62" s="40" t="s">
         <v>384</v>
-      </c>
-      <c r="C62" s="40" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="63" hidden="1" spans="1:3">
@@ -10233,10 +10230,10 @@
         <v>29</v>
       </c>
       <c r="B63" s="40" t="s">
+        <v>385</v>
+      </c>
+      <c r="C63" s="40" t="s">
         <v>386</v>
-      </c>
-      <c r="C63" s="40" t="s">
-        <v>387</v>
       </c>
     </row>
   </sheetData>
@@ -10295,7 +10292,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -10308,101 +10305,101 @@
         <v>1</v>
       </c>
       <c r="B1" s="18" t="s">
+        <v>387</v>
+      </c>
+      <c r="C1" s="18" t="s">
         <v>388</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="D1" s="18" t="s">
         <v>389</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="E1" s="18" t="s">
         <v>390</v>
-      </c>
-      <c r="E1" s="18" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:5">
       <c r="A2" s="24" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B2" s="24" t="s">
+        <v>391</v>
+      </c>
+      <c r="C2" s="24" t="s">
         <v>392</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="D2" s="24" t="s">
         <v>393</v>
       </c>
-      <c r="D2" s="24" t="s">
+      <c r="E2" s="24" t="s">
         <v>394</v>
-      </c>
-      <c r="E2" s="24" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="3" ht="25" customHeight="1" spans="1:5">
       <c r="A3" s="24" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B3" s="24" t="s">
+        <v>395</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>393</v>
+      </c>
+      <c r="D3" s="24" t="s">
         <v>396</v>
       </c>
-      <c r="C3" s="24" t="s">
-        <v>394</v>
-      </c>
-      <c r="D3" s="24" t="s">
+      <c r="E3" s="24" t="s">
         <v>397</v>
-      </c>
-      <c r="E3" s="24" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="4" ht="25" customHeight="1" spans="1:5">
       <c r="A4" s="24" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B4" s="24" t="s">
+        <v>398</v>
+      </c>
+      <c r="C4" s="24" t="s">
         <v>399</v>
       </c>
-      <c r="C4" s="24" t="s">
-        <v>400</v>
-      </c>
       <c r="D4" s="24" t="s">
+        <v>396</v>
+      </c>
+      <c r="E4" s="24" t="s">
         <v>397</v>
-      </c>
-      <c r="E4" s="24" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="5" ht="25" customHeight="1" spans="1:5">
       <c r="A5" s="24" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="6" ht="25" customHeight="1" spans="1:5">
       <c r="A6" s="24" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
   </sheetData>
@@ -10416,7 +10413,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
@@ -10426,72 +10423,72 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:4">
       <c r="A1" s="18" t="s">
+        <v>402</v>
+      </c>
+      <c r="B1" s="18" t="s">
         <v>403</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="C1" s="18" t="s">
         <v>404</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="D1" s="18" t="s">
         <v>405</v>
-      </c>
-      <c r="D1" s="18" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="2" ht="35" customHeight="1" spans="1:4">
       <c r="A2" s="22" t="s">
+        <v>406</v>
+      </c>
+      <c r="B2" s="22" t="s">
         <v>407</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="C2" s="22" t="s">
         <v>408</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="D2" s="22" t="s">
         <v>409</v>
-      </c>
-      <c r="D2" s="22" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="3" ht="35" customHeight="1" spans="1:4">
       <c r="A3" s="23" t="s">
+        <v>410</v>
+      </c>
+      <c r="B3" s="23" t="s">
         <v>411</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="C3" s="23" t="s">
         <v>412</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="D3" s="23" t="s">
         <v>413</v>
-      </c>
-      <c r="D3" s="23" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="4" ht="35" customHeight="1" spans="1:4">
       <c r="A4" s="22" t="s">
+        <v>414</v>
+      </c>
+      <c r="B4" s="22" t="s">
         <v>415</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="C4" s="22" t="s">
         <v>416</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="D4" s="22" t="s">
         <v>417</v>
-      </c>
-      <c r="D4" s="22" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="5" ht="35" customHeight="1" spans="1:4">
       <c r="A5" s="23" t="s">
+        <v>418</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>354</v>
+      </c>
+      <c r="C5" s="23" t="s">
         <v>419</v>
       </c>
-      <c r="B5" s="23" t="s">
-        <v>355</v>
-      </c>
-      <c r="C5" s="23" t="s">
+      <c r="D5" s="23" t="s">
         <v>420</v>
-      </c>
-      <c r="D5" s="23" t="s">
-        <v>421</v>
       </c>
     </row>
   </sheetData>
@@ -10505,7 +10502,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:D60"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -10515,18 +10512,18 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:4">
       <c r="A1" s="18" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="19" t="s">
+        <v>422</v>
+      </c>
+      <c r="B2" s="19" t="s">
         <v>423</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="C2" s="19" t="s">
         <v>424</v>
-      </c>
-      <c r="C2" s="19" t="s">
-        <v>425</v>
       </c>
       <c r="D2" s="19" t="s">
         <v>10</v>
@@ -10534,161 +10531,161 @@
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:4">
       <c r="A3" s="20" t="s">
+        <v>425</v>
+      </c>
+      <c r="B3" s="20" t="s">
         <v>426</v>
-      </c>
-      <c r="B3" s="20" t="s">
-        <v>427</v>
       </c>
       <c r="C3" s="20">
         <v>19</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:4">
       <c r="A4" s="21" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B4" s="21" t="s">
+        <v>428</v>
+      </c>
+      <c r="C4" s="21" t="s">
         <v>429</v>
       </c>
-      <c r="C4" s="21" t="s">
-        <v>430</v>
-      </c>
       <c r="D4" s="21" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:4">
       <c r="A5" s="20" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B5" s="20" t="s">
+        <v>430</v>
+      </c>
+      <c r="C5" s="20" t="s">
         <v>431</v>
       </c>
-      <c r="C5" s="20" t="s">
-        <v>432</v>
-      </c>
       <c r="D5" s="20" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:4">
       <c r="A6" s="21" t="s">
+        <v>432</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>426</v>
+      </c>
+      <c r="C6" s="21" t="s">
         <v>433</v>
       </c>
-      <c r="B6" s="21" t="s">
-        <v>427</v>
-      </c>
-      <c r="C6" s="21" t="s">
+      <c r="D6" s="21" t="s">
         <v>434</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:4">
       <c r="A7" s="20" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:4">
       <c r="A8" s="21" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:4">
       <c r="A9" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="B9" s="20" t="s">
         <v>438</v>
       </c>
-      <c r="B9" s="20" t="s">
+      <c r="C9" s="20" t="s">
         <v>439</v>
       </c>
-      <c r="C9" s="20" t="s">
-        <v>440</v>
-      </c>
       <c r="D9" s="20" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:4">
       <c r="A10" s="21" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B10" s="21" t="s">
+        <v>440</v>
+      </c>
+      <c r="C10" s="21" t="s">
         <v>441</v>
       </c>
-      <c r="C10" s="21" t="s">
-        <v>442</v>
-      </c>
       <c r="D10" s="21" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:4">
       <c r="A11" s="20" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B11" s="20" t="s">
+        <v>442</v>
+      </c>
+      <c r="C11" s="20" t="s">
         <v>443</v>
       </c>
-      <c r="C11" s="20" t="s">
-        <v>444</v>
-      </c>
       <c r="D11" s="20" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:4">
       <c r="A12" s="21" t="s">
+        <v>444</v>
+      </c>
+      <c r="B12" s="21" t="s">
         <v>445</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="C12" s="21" t="s">
         <v>446</v>
       </c>
-      <c r="C12" s="21" t="s">
-        <v>447</v>
-      </c>
       <c r="D12" s="21" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:4">
       <c r="A13" s="20" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:4">
       <c r="A15" s="18" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -10696,13 +10693,13 @@
         <v>0</v>
       </c>
       <c r="B16" s="19" t="s">
+        <v>449</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>424</v>
+      </c>
+      <c r="D16" s="19" t="s">
         <v>450</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>425</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1" spans="1:4">
@@ -10710,7 +10707,7 @@
         <v>1</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C17" s="20">
         <v>170.5</v>
@@ -10724,7 +10721,7 @@
         <v>2</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C18" s="21">
         <v>170.5</v>
@@ -10738,7 +10735,7 @@
         <v>3</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C19" s="20">
         <v>170.5</v>
@@ -10752,7 +10749,7 @@
         <v>4</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C20" s="21">
         <v>160</v>
@@ -10766,7 +10763,7 @@
         <v>5</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C21" s="20">
         <v>269.5</v>
@@ -10780,7 +10777,7 @@
         <v>6</v>
       </c>
       <c r="B22" s="21" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C22" s="21">
         <v>18</v>
@@ -10822,7 +10819,7 @@
         <v>9</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C25" s="20">
         <v>16.5</v>
@@ -10836,7 +10833,7 @@
         <v>10</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C26" s="21">
         <v>33</v>
@@ -10892,7 +10889,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="21" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C30" s="21">
         <v>22</v>
@@ -10920,7 +10917,7 @@
         <v>16</v>
       </c>
       <c r="B32" s="21" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C32" s="21">
         <v>8</v>
@@ -10931,18 +10928,18 @@
     </row>
     <row r="34" ht="22" customHeight="1" spans="1:4">
       <c r="A34" s="18" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="19" t="s">
+        <v>422</v>
+      </c>
+      <c r="B35" s="19" t="s">
         <v>423</v>
       </c>
-      <c r="B35" s="19" t="s">
+      <c r="C35" s="19" t="s">
         <v>424</v>
-      </c>
-      <c r="C35" s="19" t="s">
-        <v>425</v>
       </c>
       <c r="D35" s="19" t="s">
         <v>10</v>
@@ -10950,329 +10947,329 @@
     </row>
     <row r="36" ht="18" customHeight="1" spans="1:4">
       <c r="A36" s="20" t="s">
+        <v>462</v>
+      </c>
+      <c r="B36" s="20" t="s">
         <v>463</v>
       </c>
-      <c r="B36" s="20" t="s">
+      <c r="C36" s="20" t="s">
+        <v>446</v>
+      </c>
+      <c r="D36" s="20" t="s">
         <v>464</v>
-      </c>
-      <c r="C36" s="20" t="s">
-        <v>447</v>
-      </c>
-      <c r="D36" s="20" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1" spans="1:4">
       <c r="A37" s="21" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B37" s="21" t="s">
+        <v>465</v>
+      </c>
+      <c r="C37" s="21" t="s">
         <v>466</v>
       </c>
-      <c r="C37" s="21" t="s">
+      <c r="D37" s="21" t="s">
         <v>467</v>
-      </c>
-      <c r="D37" s="21" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1" spans="1:4">
       <c r="A38" s="20" t="s">
+        <v>425</v>
+      </c>
+      <c r="B38" s="20" t="s">
         <v>426</v>
       </c>
-      <c r="B38" s="20" t="s">
+      <c r="C38" s="20" t="s">
+        <v>468</v>
+      </c>
+      <c r="D38" s="20" t="s">
         <v>427</v>
-      </c>
-      <c r="C38" s="20" t="s">
-        <v>469</v>
-      </c>
-      <c r="D38" s="20" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1" spans="1:4">
       <c r="A39" s="21" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B39" s="21" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D39" s="21" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1" spans="1:4">
       <c r="A40" s="20" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D40" s="20" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1" spans="1:4">
       <c r="A41" s="21" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B41" s="21" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D41" s="21" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1" spans="1:4">
       <c r="A42" s="20" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B42" s="20" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C42" s="20" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D42" s="20" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1" spans="1:4">
       <c r="A43" s="21" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B43" s="21" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D43" s="21" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1" spans="1:4">
       <c r="A44" s="20" t="s">
+        <v>473</v>
+      </c>
+      <c r="B44" s="20" t="s">
         <v>474</v>
       </c>
-      <c r="B44" s="20" t="s">
+      <c r="C44" s="20" t="s">
+        <v>393</v>
+      </c>
+      <c r="D44" s="20" t="s">
         <v>475</v>
-      </c>
-      <c r="C44" s="20" t="s">
-        <v>394</v>
-      </c>
-      <c r="D44" s="20" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1" spans="1:4">
       <c r="A46" s="18" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="19" t="s">
+        <v>422</v>
+      </c>
+      <c r="B47" s="19" t="s">
         <v>423</v>
       </c>
-      <c r="B47" s="19" t="s">
+      <c r="C47" s="19" t="s">
         <v>424</v>
       </c>
-      <c r="C47" s="19" t="s">
-        <v>425</v>
-      </c>
       <c r="D47" s="19" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1" spans="1:4">
       <c r="A48" s="20" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B48" s="20" t="s">
+        <v>478</v>
+      </c>
+      <c r="C48" s="20" t="s">
         <v>479</v>
       </c>
-      <c r="C48" s="20" t="s">
+      <c r="D48" s="20" t="s">
         <v>480</v>
-      </c>
-      <c r="D48" s="20" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1" spans="1:4">
       <c r="A49" s="21" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B49" s="21" t="s">
+        <v>481</v>
+      </c>
+      <c r="C49" s="21" t="s">
         <v>482</v>
       </c>
-      <c r="C49" s="21" t="s">
+      <c r="D49" s="21" t="s">
         <v>483</v>
-      </c>
-      <c r="D49" s="21" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1" spans="1:4">
       <c r="A50" s="20" t="s">
+        <v>425</v>
+      </c>
+      <c r="B50" s="20" t="s">
         <v>426</v>
       </c>
-      <c r="B50" s="20" t="s">
-        <v>427</v>
-      </c>
       <c r="C50" s="20" t="s">
+        <v>484</v>
+      </c>
+      <c r="D50" s="20" t="s">
         <v>485</v>
-      </c>
-      <c r="D50" s="20" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1" spans="1:4">
       <c r="A51" s="21" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B51" s="21" t="s">
+        <v>428</v>
+      </c>
+      <c r="C51" s="21" t="s">
+        <v>468</v>
+      </c>
+      <c r="D51" s="21" t="s">
         <v>429</v>
-      </c>
-      <c r="C51" s="21" t="s">
-        <v>469</v>
-      </c>
-      <c r="D51" s="21" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1" spans="1:4">
       <c r="A52" s="20" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B52" s="20" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C52" s="20" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D52" s="20" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1" spans="1:4">
       <c r="A53" s="21" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B53" s="21" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C53" s="21" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="D53" s="21" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1" spans="1:4">
       <c r="A54" s="20" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B54" s="20" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C54" s="20" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D54" s="20" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1" spans="1:4">
       <c r="A55" s="21" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B55" s="21" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C55" s="21" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="D55" s="21" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1" spans="1:4">
       <c r="A56" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="B56" s="20" t="s">
         <v>438</v>
       </c>
-      <c r="B56" s="20" t="s">
-        <v>439</v>
-      </c>
       <c r="C56" s="20" t="s">
+        <v>490</v>
+      </c>
+      <c r="D56" s="20" t="s">
         <v>491</v>
-      </c>
-      <c r="D56" s="20" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1" spans="1:4">
       <c r="A57" s="21" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B57" s="21" t="s">
+        <v>440</v>
+      </c>
+      <c r="C57" s="21" t="s">
+        <v>439</v>
+      </c>
+      <c r="D57" s="21" t="s">
         <v>441</v>
-      </c>
-      <c r="C57" s="21" t="s">
-        <v>440</v>
-      </c>
-      <c r="D57" s="21" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1" spans="1:4">
       <c r="A58" s="20" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B58" s="20" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C58" s="20" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D58" s="20" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1" spans="1:4">
       <c r="A59" s="21" t="s">
+        <v>444</v>
+      </c>
+      <c r="B59" s="21" t="s">
         <v>445</v>
       </c>
-      <c r="B59" s="21" t="s">
+      <c r="C59" s="21" t="s">
+        <v>493</v>
+      </c>
+      <c r="D59" s="21" t="s">
         <v>446</v>
-      </c>
-      <c r="C59" s="21" t="s">
-        <v>494</v>
-      </c>
-      <c r="D59" s="21" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1" spans="1:4">
       <c r="A60" s="20" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B60" s="20" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C60" s="20" t="s">
+        <v>490</v>
+      </c>
+      <c r="D60" s="20" t="s">
         <v>491</v>
-      </c>
-      <c r="D60" s="20" t="s">
-        <v>492</v>
       </c>
     </row>
   </sheetData>
@@ -11286,7 +11283,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="16384" width="9" style="17"/>
   </cols>
@@ -11301,7 +11298,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="16384" width="9" style="17"/>
   </cols>
@@ -11316,7 +11313,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="16384" width="9" style="17"/>
   </cols>
